--- a/output_data/DC_Load_OG.xlsx
+++ b/output_data/DC_Load_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.1188024998786</v>
+        <v>25.2091678731138</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.25680152818898</v>
+        <v>20.19224600560987</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.71427179904808</v>
+        <v>15.77336610137357</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.57576930537962</v>
+        <v>27.069157562994</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.53084903395421</v>
+        <v>53.18627060447989</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.31177412848119</v>
+        <v>146.2887723710159</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70.53379350705541</v>
+        <v>387.9752177286161</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>148.0211337943819</v>
+        <v>865.6168777173214</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>231.0641250546182</v>
+        <v>1491.58298619758</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>326.0264177808915</v>
+        <v>2105.652778042698</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>345.5623707908874</v>
+        <v>2523.172946426085</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>327.6334612366682</v>
+        <v>2338.169736248886</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>292.0120742516069</v>
+        <v>1928.913754802</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>246.2997962453502</v>
+        <v>1442.602619601363</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>212.7574899032609</v>
+        <v>1129.073120477153</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>199.2983166597962</v>
+        <v>1035.897411953538</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>206.2731702982554</v>
+        <v>1307.210260879144</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>227.1223946686046</v>
+        <v>1479.72062508854</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>233.4111895445607</v>
+        <v>1662.742956850917</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>237.2250923354355</v>
+        <v>1689.979125600758</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>216.2279763454046</v>
+        <v>1532.935419255351</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>186.0071436574962</v>
+        <v>1284.567003843466</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>143.7415417763294</v>
+        <v>968.9314184588479</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>91.71810434369928</v>
+        <v>632.0843328914225</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>240</v>
+        <v>2040</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_Load_OG.xlsx
+++ b/output_data/DC_Load_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.2091678731138</v>
+        <v>25.97504401650553</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.19224600560987</v>
+        <v>20.20267432110311</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.77336610137357</v>
+        <v>13.86215176570172</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.069157562994</v>
+        <v>20.40243506959648</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.18627060447989</v>
+        <v>30.64339425972503</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146.2887723710159</v>
+        <v>74.22784275486978</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>387.9752177286161</v>
+        <v>155.324432520392</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>865.6168777173214</v>
+        <v>325.2923709299901</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1491.58298619758</v>
+        <v>585.5291055395354</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2105.652778042698</v>
+        <v>812.0463246236103</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2523.172946426085</v>
+        <v>936.296824770001</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2338.169736248886</v>
+        <v>823.5709313094196</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1928.913754802</v>
+        <v>718.8998831885627</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1442.602619601363</v>
+        <v>566.5481722033031</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1129.073120477153</v>
+        <v>432.1506003647342</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1035.897411953538</v>
+        <v>426.8932923317359</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1307.210260879144</v>
+        <v>502.2405871621478</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1479.72062508854</v>
+        <v>549.6342197909921</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1662.742956850917</v>
+        <v>635.7657517577202</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1689.979125600758</v>
+        <v>579.319431834013</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1532.935419255351</v>
+        <v>563.2319510538875</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1284.567003843466</v>
+        <v>450.9749962662844</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>968.9314184588479</v>
+        <v>337.1690468421854</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>632.0843328914225</v>
+        <v>240.8134690757525</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2040</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_Load_OG.xlsx
+++ b/output_data/DC_Load_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.97504401650553</v>
+        <v>26.01504401650553</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.86215176570172</v>
+        <v>13.42215176570172</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.40243506959648</v>
+        <v>18.00243506959648</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.64339425972503</v>
+        <v>35.76339425972503</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>74.22784275486978</v>
+        <v>66.34784275486979</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155.324432520392</v>
+        <v>175.524432520392</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>325.2923709299901</v>
+        <v>348.77237092999</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>585.5291055395354</v>
+        <v>634.3691055395354</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>812.0463246236103</v>
+        <v>823.2863246236103</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>936.296824770001</v>
+        <v>879.9368247700011</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>823.5709313094196</v>
+        <v>840.2109313094197</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>718.8998831885627</v>
+        <v>682.3798831885628</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>566.5481722033031</v>
+        <v>545.508172203303</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>432.1506003647342</v>
+        <v>429.0706003647342</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>426.8932923317359</v>
+        <v>408.7332923317359</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>502.2405871621478</v>
+        <v>460.1205871621478</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>549.6342197909921</v>
+        <v>574.994219790992</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>635.7657517577202</v>
+        <v>614.7257517577202</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>579.319431834013</v>
+        <v>623.5994318340131</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>563.2319510538875</v>
+        <v>551.1519510538875</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>450.9749962662844</v>
+        <v>466.4549962662845</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>337.1690468421854</v>
+        <v>328.4490468421853</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>240.8134690757525</v>
+        <v>255.3734690757525</v>
       </c>
     </row>
     <row r="26">

--- a/output_data/DC_Load_OG.xlsx
+++ b/output_data/DC_Load_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.01504401650553</v>
+        <v>25.41504401650553</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.42215176570172</v>
+        <v>14.74215176570172</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.00243506959648</v>
+        <v>19.24243506959648</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.76339425972503</v>
+        <v>34.48339425972503</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>66.34784275486979</v>
+        <v>67.18784275486979</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175.524432520392</v>
+        <v>176.244432520392</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>348.77237092999</v>
+        <v>349.65237092999</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>634.3691055395354</v>
+        <v>594.7691055395354</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>823.2863246236103</v>
+        <v>779.5663246236103</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>879.9368247700011</v>
+        <v>904.8168247700011</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>840.2109313094197</v>
+        <v>841.4109313094197</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>682.3798831885628</v>
+        <v>716.4198831885627</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>545.508172203303</v>
+        <v>537.1881722033031</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>429.0706003647342</v>
+        <v>429.2706003647342</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>408.7332923317359</v>
+        <v>399.1732923317359</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>460.1205871621478</v>
+        <v>488.3605871621478</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>574.994219790992</v>
+        <v>576.474219790992</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>614.7257517577202</v>
+        <v>618.1257517577202</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>623.5994318340131</v>
+        <v>605.959431834013</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>551.1519510538875</v>
+        <v>571.2319510538875</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>466.4549962662845</v>
+        <v>437.4549962662845</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>328.4490468421853</v>
+        <v>362.8090468421854</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>255.3734690757525</v>
+        <v>213.6934690757525</v>
       </c>
     </row>
     <row r="26">
